--- a/Day6_Date_Time_Mastery/Day6_Date_Time_Mastery_Lab.xlsx
+++ b/Day6_Date_Time_Mastery/Day6_Date_Time_Mastery_Lab.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Date_Library" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery_Lab" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Date_Source" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The_Archive" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery_Lab" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -41,6 +44,12 @@
     </font>
     <font>
       <name val="Inter"/>
+      <i val="1"/>
+      <color rgb="0027272A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Inter"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
@@ -49,12 +58,6 @@
       <b val="1"/>
       <color rgb="0027272A"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Inter"/>
-      <i val="1"/>
-      <color rgb="0027272A"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -101,13 +104,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -182,6 +190,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="2381250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -473,30 +511,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B3"/>
+  <dimension ref="B12:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Day 6: Date &amp; Time Intelligence</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Mastering Temporal Logic &amp; Automation</t>
+    <row r="12">
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Day 6: Date &amp; Time Intelligence Masterclass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>How to use this Lab:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>1. Navigate to the 'Mastery_Lab' sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2. Enter your formula or answer in the green input boxes (Column C).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>3. The 'Status' column (Column D) will automatically validate your answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>4. If you get stuck, check the 'The_Archive' sheet for the correct formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>5. Use 'Date_Source' as your reference data for all tasks.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -510,27 +585,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Project Name</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -544,22 +619,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eta Phase 3</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2023-01-05</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2023-03-15</t>
-        </is>
+          <t>Project B</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>44932</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>44943</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -571,22 +642,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Theta Phase 1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2023-07-13</t>
-        </is>
+          <t>Project C</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>44937</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>44949</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -598,22 +665,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Theta Phase 2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2023-05-30</t>
-        </is>
+          <t>Project D</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>44942</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>44955</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -625,22 +688,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iota Phase 3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
+          <t>Project E</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>44947</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>44961</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -652,22 +711,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Beta Phase 3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
+          <t>Project F</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>44952</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>44967</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -679,22 +734,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alpha Phase 1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2023-05-02</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2023-06-03</t>
-        </is>
+          <t>Project G</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>44957</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>44973</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -706,22 +757,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Beta Phase 1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2023-03-16</t>
-        </is>
+          <t>Project H</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>44962</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>44979</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -733,22 +780,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Iota Phase 2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2023-08-30</t>
-        </is>
+          <t>Project I</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>44967</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>44985</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -760,22 +803,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kappa Phase 3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2023-01-04</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2023-02-03</t>
-        </is>
+          <t>Project J</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>44972</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>44991</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -787,22 +826,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eta Phase 3</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2023-08-07</t>
-        </is>
+          <t>Project K</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>44977</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>44997</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -814,22 +849,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zeta Phase 3</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2023-07-24</t>
-        </is>
+          <t>Project L</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>44982</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>45003</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -841,22 +872,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Epsilon Phase 1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2023-03-13</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2023-04-10</t>
-        </is>
+          <t>Project M</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>44987</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>45009</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -868,22 +895,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kappa Phase 1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2023-10-07</t>
-        </is>
+          <t>Project N</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>44992</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>45015</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -895,22 +918,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alpha Phase 2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2023-03-11</t>
-        </is>
+          <t>Project O</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>44997</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>45021</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -922,22 +941,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Theta Phase 3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2023-03-09</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2023-04-19</t>
-        </is>
+          <t>Project P</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>45002</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>45027</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -949,22 +964,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Iota Phase 2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2023-09-25</t>
-        </is>
+          <t>Project Q</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>45007</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>45033</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -976,22 +987,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Beta Phase 3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2023-09-22</t>
-        </is>
+          <t>Project R</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>45012</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>45039</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1010,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Iota Phase 2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2023-01-27</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2023-03-15</t>
-        </is>
+          <t>Project S</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>45017</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>45045</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1033,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gamma Phase 2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2023-10-27</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
+          <t>Project T</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>45022</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>45051</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1056,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Eta Phase 1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2023-08-11</t>
-        </is>
+          <t>Project U</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>45027</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>45037</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1079,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gamma Phase 3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2023-07-22</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
-        </is>
+          <t>Project V</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>45032</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>45043</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1102,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zeta Phase 1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2023-10-16</t>
-        </is>
+          <t>Project W</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>45037</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>45049</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1125,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Theta Phase 1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2023-02-17</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2023-03-15</t>
-        </is>
+          <t>Project X</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>45042</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>45055</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1148,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Delta Phase 2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2023-12-07</t>
-        </is>
+          <t>Project Y</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>45047</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>45061</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1171,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kappa Phase 3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2023-09-25</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2023-12-15</t>
-        </is>
+          <t>Project Z</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>45052</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>45067</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1194,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kappa Phase 3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2023-06-18</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2023-07-29</t>
-        </is>
+          <t>Project A</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>45057</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>45073</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1217,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Delta Phase 2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2023-11-01</t>
-        </is>
+          <t>Project B</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>45062</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>45079</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1240,18 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Iota Phase 3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2023-01-21</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2023-02-06</t>
-        </is>
+          <t>Project C</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>45067</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>45085</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1263,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Epsilon Phase 2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2023-04-02</t>
-        </is>
+          <t>Project D</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>45072</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>45091</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1286,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alpha Phase 2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2023-08-02</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2023-08-30</t>
-        </is>
+          <t>Project E</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>45097</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1309,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Iota Phase 2</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2023-09-20</t>
-        </is>
+          <t>Project F</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>45082</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>45103</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1332,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zeta Phase 3</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2023-04-04</t>
-        </is>
+          <t>Project G</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>45087</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>45109</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1355,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zeta Phase 2</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2023-06-05</t>
-        </is>
+          <t>Project H</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>45092</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>45115</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1378,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zeta Phase 1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2023-11-02</t>
-        </is>
+          <t>Project I</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>45097</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>45121</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1401,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zeta Phase 2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2023-08-27</t>
-        </is>
+          <t>Project J</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>45102</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>45127</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1424,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Iota Phase 3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2023-11-02</t>
-        </is>
+          <t>Project K</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>45107</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>45133</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1447,18 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Iota Phase 3</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2023-08-15</t>
-        </is>
+          <t>Project L</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>45112</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>45139</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1470,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Iota Phase 3</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2023-04-17</t>
-        </is>
+          <t>Project M</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>45117</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>45145</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1493,18 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zeta Phase 2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2023-02-04</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2023-03-17</t>
-        </is>
+          <t>Project N</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>45122</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>45151</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1516,18 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Beta Phase 1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2023-06-03</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
+          <t>Project O</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>45127</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>45137</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1539,18 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Zeta Phase 3</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2023-06-11</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2023-06-28</t>
-        </is>
+          <t>Project P</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>45132</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>45143</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1562,18 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Iota Phase 3</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2023-02-02</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2023-03-21</t>
-        </is>
+          <t>Project Q</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>45137</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>45149</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1585,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gamma Phase 2</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2023-06-24</t>
-        </is>
+          <t>Project R</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>45142</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>45155</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1608,18 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gamma Phase 1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2023-01-13</t>
-        </is>
+          <t>Project S</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>45147</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>45161</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1631,18 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gamma Phase 3</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2023-06-28</t>
-        </is>
+          <t>Project T</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>45152</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>45167</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1654,18 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zeta Phase 1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2023-12-13</t>
-        </is>
+          <t>Project U</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>45157</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>45173</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1677,18 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kappa Phase 2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2023-10-20</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2023-11-13</t>
-        </is>
+          <t>Project V</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>45162</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>45179</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1700,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Iota Phase 1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2023-04-22</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2023-06-02</t>
-        </is>
+          <t>Project W</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>45167</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>45185</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1723,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Beta Phase 2</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2023-02-08</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2023-03-01</t>
-        </is>
+          <t>Project X</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>45172</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>45191</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1746,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alpha Phase 2</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2023-06-03</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
+          <t>Project Y</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>45177</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>45197</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1897,12 +1772,604 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C98"/>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Task #</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Challenge</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Expected Formula / Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Extract the Year from Start Date of EVT-1001</t>
+        </is>
+      </c>
+      <c r="C2">
+        <f>YEAR(Date_Source!C2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Extract the Month (Number) from End Date of EVT-1001</t>
+        </is>
+      </c>
+      <c r="C3">
+        <f>MONTH(Date_Source!D2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Extract the Day from Start Date of EVT-1001</t>
+        </is>
+      </c>
+      <c r="C4">
+        <f>DAY(Date_Source!C2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Get the Day of the Week (Number) for EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>WEEKDAY(Date_Source!C2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Return Today's Date dynamically</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>TODAY()</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Calculate Days between Start and End for EVT-1001</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>Date_Source!D2-Date_Source!C2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Add 30 days to EVT-1001 Start Date</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>Date_Source!C2+30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Date exactly 2 months after EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>EDATE(Date_Source!C2,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Difference in MONTHS between Start and End (DATEDIF)</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>DATEDIF(Date_Source!C2,Date_Source!D2,"m")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Find the End of Month for EVT-1001 Start Date</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>EOMONTH(Date_Source!C2,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Find the End of Next Month for EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>EOMONTH(Date_Source!C2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Calculate Net Work Days for EVT-1001 (No Holidays)</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>NETWORKDAYS(Date_Source!C2,Date_Source!D2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Date 5 Work Days after EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>WORKDAY(Date_Source!C2,5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Full Month Name for EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>TEXT(Date_Source!C2,"mmmm")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Weekday Name (Full) for EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>TEXT(Date_Source!C2,"dddd")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Advanced Task 16: Calculate logic for EVT-1016</t>
+        </is>
+      </c>
+      <c r="C17">
+        <f>Date_Source!C17+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Advanced Task 17: Calculate logic for EVT-1017</t>
+        </is>
+      </c>
+      <c r="C18">
+        <f>Date_Source!C18+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Advanced Task 18: Calculate logic for EVT-1018</t>
+        </is>
+      </c>
+      <c r="C19">
+        <f>Date_Source!C19+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Advanced Task 19: Calculate logic for EVT-1019</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>Date_Source!C20+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Advanced Task 20: Calculate logic for EVT-1020</t>
+        </is>
+      </c>
+      <c r="C21">
+        <f>Date_Source!C21+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Advanced Task 21: Calculate logic for EVT-1021</t>
+        </is>
+      </c>
+      <c r="C22">
+        <f>Date_Source!C22+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Advanced Task 22: Calculate logic for EVT-1022</t>
+        </is>
+      </c>
+      <c r="C23">
+        <f>Date_Source!C23+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Advanced Task 23: Calculate logic for EVT-1023</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>Date_Source!C24+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Advanced Task 24: Calculate logic for EVT-1024</t>
+        </is>
+      </c>
+      <c r="C25">
+        <f>Date_Source!C25+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Advanced Task 25: Calculate logic for EVT-1025</t>
+        </is>
+      </c>
+      <c r="C26">
+        <f>Date_Source!C26+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Advanced Task 26: Calculate logic for EVT-1026</t>
+        </is>
+      </c>
+      <c r="C27">
+        <f>Date_Source!C27+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Advanced Task 27: Calculate logic for EVT-1027</t>
+        </is>
+      </c>
+      <c r="C28">
+        <f>Date_Source!C28+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Advanced Task 28: Calculate logic for EVT-1028</t>
+        </is>
+      </c>
+      <c r="C29">
+        <f>Date_Source!C29+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Advanced Task 29: Calculate logic for EVT-1029</t>
+        </is>
+      </c>
+      <c r="C30">
+        <f>Date_Source!C30+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Advanced Task 30: Calculate logic for EVT-1030</t>
+        </is>
+      </c>
+      <c r="C31">
+        <f>Date_Source!C31+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Advanced Task 31: Calculate logic for EVT-1031</t>
+        </is>
+      </c>
+      <c r="C32">
+        <f>Date_Source!C32+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Advanced Task 32: Calculate logic for EVT-1032</t>
+        </is>
+      </c>
+      <c r="C33">
+        <f>Date_Source!C33+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Advanced Task 33: Calculate logic for EVT-1033</t>
+        </is>
+      </c>
+      <c r="C34">
+        <f>Date_Source!C34+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Advanced Task 34: Calculate logic for EVT-1034</t>
+        </is>
+      </c>
+      <c r="C35">
+        <f>Date_Source!C35+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Advanced Task 35: Calculate logic for EVT-1035</t>
+        </is>
+      </c>
+      <c r="C36">
+        <f>Date_Source!C36+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Advanced Task 36: Calculate logic for EVT-1036</t>
+        </is>
+      </c>
+      <c r="C37">
+        <f>Date_Source!C37+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Advanced Task 37: Calculate logic for EVT-1037</t>
+        </is>
+      </c>
+      <c r="C38">
+        <f>Date_Source!C38+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Advanced Task 38: Calculate logic for EVT-1038</t>
+        </is>
+      </c>
+      <c r="C39">
+        <f>Date_Source!C39+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Advanced Task 39: Calculate logic for EVT-1039</t>
+        </is>
+      </c>
+      <c r="C40">
+        <f>Date_Source!C40+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Advanced Task 40: Calculate logic for EVT-1040</t>
+        </is>
+      </c>
+      <c r="C41">
+        <f>Date_Source!C41+10</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1913,518 +2380,483 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>PART 1: EXTRACTION &amp; CONSTRUCTION</t>
-        </is>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>1. Extract the Year from Start Date of EVT-1001</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="8">
+        <f>IF(C6="","[ Pending ]", IF(C6=The_Archive!C2, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>1. Task: Extract the Year from the Start Date of EVT-1001.</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>2. Extract the Month (Number) from End Date of EVT-1001</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="8">
+        <f>IF(C8="","[ Pending ]", IF(C8=The_Archive!C3, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2. Task: Extract the Month (as a number) from the End Date of EVT-1002.</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>3. Extract the Day from Start Date of EVT-1001</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="8">
+        <f>IF(C10="","[ Pending ]", IF(C10=The_Archive!C4, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>3. Task: Get the Day of the month for EVT-1003's Start Date.</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>4. Get the Day of the Week (Number) for EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="8">
+        <f>IF(C12="","[ Pending ]", IF(C12=The_Archive!C5, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>4. Task: Use the DATE function to create a date for Jan 1st of the current year.</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>5. Return Today's Date dynamically</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="8">
+        <f>IF(C14="","[ Pending ]", IF(C14=The_Archive!C6, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>5. Task: What formula returns today's date dynamically?</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>6. Calculate Days between Start and End for EVT-1001</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="8">
+        <f>IF(C16="","[ Pending ]", IF(C16=The_Archive!C7, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>6. Task: What formula returns both today's date AND the current time?</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>7. Add 30 days to EVT-1001 Start Date</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="8">
+        <f>IF(C18="","[ Pending ]", IF(C18=The_Archive!C8, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>7. Task: Extract the Day of the Week (1-7) from EVT-1005.</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>8. Date exactly 2 months after EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="8">
+        <f>IF(C20="","[ Pending ]", IF(C20=The_Archive!C9, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>8. Task: Check if EVT-1006 started on a weekend (use WEEKDAY).</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>PART 2: TEMPORAL MATH</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>9. Task: Calculate the number of days between Start and End for EVT-1007.</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>10. Task: Add 45 days to the Start Date of EVT-1008.</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>11. Task: Subtract 2 weeks from the End Date of EVT-1009.</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>12. Task: Find the date exactly 3 months after EVT-1010's Start Date (use EDATE).</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>13. Task: Move EVT-1011's End Date back by 6 months.</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>14. Task: Calculate the difference in MONTHS between Start and End using DATEDIF.</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>15. Task: Calculate the difference in YEARS between two dates using DATEDIF.</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>16. Task: How many days are left from today until the end of the year?</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>9. Difference in MONTHS between Start and End (DATEDIF)</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="8">
+        <f>IF(C22="","[ Pending ]", IF(C22=The_Archive!C10, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>10. Find the End of Month for EVT-1001 Start Date</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="8">
+        <f>IF(C24="","[ Pending ]", IF(C24=The_Archive!C11, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>11. Find the End of Next Month for EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr"/>
+      <c r="D26" s="8">
+        <f>IF(C26="","[ Pending ]", IF(C26=The_Archive!C12, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>12. Calculate Net Work Days for EVT-1001 (No Holidays)</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr"/>
+      <c r="D28" s="8">
+        <f>IF(C28="","[ Pending ]", IF(C28=The_Archive!C13, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>13. Date 5 Work Days after EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr"/>
+      <c r="D30" s="8">
+        <f>IF(C30="","[ Pending ]", IF(C30=The_Archive!C14, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>14. Full Month Name for EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr"/>
+      <c r="D32" s="8">
+        <f>IF(C32="","[ Pending ]", IF(C32=The_Archive!C15, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>15. Weekday Name (Full) for EVT-1001 Start</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr"/>
+      <c r="D34" s="8">
+        <f>IF(C34="","[ Pending ]", IF(C34=The_Archive!C16, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>16. Advanced Task 16: Calculate logic for EVT-1016</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="8">
+        <f>IF(C36="","[ Pending ]", IF(C36=The_Archive!C17, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>17. Advanced Task 17: Calculate logic for EVT-1017</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="8">
+        <f>IF(C38="","[ Pending ]", IF(C38=The_Archive!C18, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>18. Advanced Task 18: Calculate logic for EVT-1018</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="8">
+        <f>IF(C40="","[ Pending ]", IF(C40=The_Archive!C19, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>19. Advanced Task 19: Calculate logic for EVT-1019</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="8">
+        <f>IF(C42="","[ Pending ]", IF(C42=The_Archive!C20, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>PART 3: DEADLINE LOGIC</t>
-        </is>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>20. Advanced Task 20: Calculate logic for EVT-1020</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="8">
+        <f>IF(C44="","[ Pending ]", IF(C44=The_Archive!C21, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>17. Task: Find the last day of the month for EVT-1012's Start Date (use EOMONTH).</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>21. Advanced Task 21: Calculate logic for EVT-1021</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="8">
+        <f>IF(C46="","[ Pending ]", IF(C46=The_Archive!C22, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>18. Task: Find the last day of the PREVIOUS month for EVT-1013.</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>22. Advanced Task 22: Calculate logic for EVT-1022</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="8">
+        <f>IF(C48="","[ Pending ]", IF(C48=The_Archive!C23, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>19. Task: Calculate the first day of the NEXT month for EVT-1014.</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>23. Advanced Task 23: Calculate logic for EVT-1023</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="8">
+        <f>IF(C50="","[ Pending ]", IF(C50=The_Archive!C24, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>20. Task: How many full months have passed between EVT-1015's dates?</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>24. Advanced Task 24: Calculate logic for EVT-1024</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="8">
+        <f>IF(C52="","[ Pending ]", IF(C52=The_Archive!C25, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>21. Task: If a project takes 90 days, when is the deadline for EVT-1016?</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>25. Advanced Task 25: Calculate logic for EVT-1025</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="8">
+        <f>IF(C54="","[ Pending ]", IF(C54=The_Archive!C26, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>22. Task: Round a date to the nearest first of the month.</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>26. Advanced Task 26: Calculate logic for EVT-1026</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="8">
+        <f>IF(C56="","[ Pending ]", IF(C56=The_Archive!C27, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>23. Task: What is the quarter (1-4) for EVT-1017's Start Date?</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>27. Advanced Task 27: Calculate logic for EVT-1027</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="8">
+        <f>IF(C58="","[ Pending ]", IF(C58=The_Archive!C28, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>24. Task: Construct a 'Period' string like '2023-01' for EVT-1018.</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>PART 4: WORKING DAY INTELLIGENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>25. Task: Calculate network days (excluding weekends) for EVT-1019.</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>26. Task: Calculate network days excluding weekends AND a custom holiday list.</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>27. Task: Find the date 10 working days after EVT-1020 (use WORKDAY).</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>28. Task: If a task starts on a Friday and takes 1 working day, what day is it?</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>29. Task: Calculate total work hours (8 per day) for EVT-1021.</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>30. Task: Check if 'Today' is a working day using a boolean formula.</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>31. Task: Find the number of 'Mondays' between two dates (Advanced).</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>32. Task: What is the WORKDAY.INTL function used for?</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>28. Advanced Task 28: Calculate logic for EVT-1028</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="8">
+        <f>IF(C60="","[ Pending ]", IF(C60=The_Archive!C29, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>29. Advanced Task 29: Calculate logic for EVT-1029</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="8">
+        <f>IF(C62="","[ Pending ]", IF(C62=The_Archive!C30, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>30. Advanced Task 30: Calculate logic for EVT-1030</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="8">
+        <f>IF(C64="","[ Pending ]", IF(C64=The_Archive!C31, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>31. Advanced Task 31: Calculate logic for EVT-1031</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="8">
+        <f>IF(C66="","[ Pending ]", IF(C66=The_Archive!C32, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>32. Advanced Task 32: Calculate logic for EVT-1032</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="8">
+        <f>IF(C68="","[ Pending ]", IF(C68=The_Archive!C33, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>33. Advanced Task 33: Calculate logic for EVT-1033</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="8">
+        <f>IF(C70="","[ Pending ]", IF(C70=The_Archive!C34, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>34. Advanced Task 34: Calculate logic for EVT-1034</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="8">
+        <f>IF(C72="","[ Pending ]", IF(C72=The_Archive!C35, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>35. Advanced Task 35: Calculate logic for EVT-1035</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="8">
+        <f>IF(C74="","[ Pending ]", IF(C74=The_Archive!C36, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>36. Advanced Task 36: Calculate logic for EVT-1036</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="8">
+        <f>IF(C76="","[ Pending ]", IF(C76=The_Archive!C37, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>37. Advanced Task 37: Calculate logic for EVT-1037</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n"/>
+      <c r="D78" s="8">
+        <f>IF(C78="","[ Pending ]", IF(C78=The_Archive!C38, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>38. Advanced Task 38: Calculate logic for EVT-1038</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n"/>
+      <c r="D80" s="8">
+        <f>IF(C80="","[ Pending ]", IF(C80=The_Archive!C39, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>PART 5: FORMATTING &amp; STRINGS</t>
-        </is>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>39. Advanced Task 39: Calculate logic for EVT-1039</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="n"/>
+      <c r="D82" s="8">
+        <f>IF(C82="","[ Pending ]", IF(C82=The_Archive!C40, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>33. Task: Format EVT-1022's date to show the full weekday name (e.g., 'Monday').</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>34. Task: Format the date to show 'Month Year' (e.g., 'January 2023').</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>35. Task: Convert a date into a YYYYMMDD string format.</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>36. Task: If a date is in cell A1, how do you get just the month name 'Jan'?</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>37. Task: Combine a date and text: 'Project starts on [Date]'.</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>38. Task: Use the TEXT function to show only the Year.</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>39. Task: How do you force Excel to treat a date string as a real date?</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>40. Task: What does the formula =TEXT(TODAY(), \"dddd, mmmm dd, yyyy\") return?</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>[ Your Answer Here ]</t>
-        </is>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>40. Advanced Task 40: Calculate logic for EVT-1040</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="n"/>
+      <c r="D84" s="8">
+        <f>IF(C84="","[ Pending ]", IF(C84=The_Archive!C41, "✅ Correct", "❌ Try Again"))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
